--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO_Pretty.xlsx
@@ -1261,7 +1261,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="3">
@@ -1312,7 +1312,7 @@
         <v>3</v>
       </c>
       <c r="M3" s="47" t="n">
-        <v>263</v>
+        <v>72698</v>
       </c>
     </row>
     <row r="4">
@@ -1363,7 +1363,7 @@
         <v>0</v>
       </c>
       <c r="M4" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="5">
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="M5" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="6">
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="52" t="n">
-        <v>283</v>
+        <v>24398</v>
       </c>
     </row>
     <row r="7">
@@ -1516,7 +1516,7 @@
         <v>4</v>
       </c>
       <c r="M7" s="47" t="n">
-        <v>480</v>
+        <v>47539</v>
       </c>
     </row>
     <row r="8">
@@ -1567,7 +1567,7 @@
         <v>4</v>
       </c>
       <c r="M8" s="52" t="n">
-        <v>480</v>
+        <v>47539</v>
       </c>
     </row>
     <row r="9">
@@ -1618,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="M9" s="47" t="n">
-        <v>346</v>
+        <v>77689</v>
       </c>
     </row>
     <row r="10">
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="52" t="n">
-        <v>379</v>
+        <v>114580</v>
       </c>
     </row>
     <row r="11">
@@ -1720,7 +1720,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M12" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="13">
@@ -1822,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="M13" s="47" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="14">
@@ -1873,7 +1873,7 @@
         <v>5</v>
       </c>
       <c r="M14" s="52" t="n">
-        <v>865</v>
+        <v>73567</v>
       </c>
     </row>
     <row r="15">
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="16">
@@ -1975,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="52" t="n">
-        <v>613</v>
+        <v>123384</v>
       </c>
     </row>
     <row r="17">
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="M17" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="18">
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="M18" s="52" t="n">
-        <v>343</v>
+        <v>96138</v>
       </c>
     </row>
     <row r="19">
@@ -2128,7 +2128,7 @@
         <v>3</v>
       </c>
       <c r="M19" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="20">
@@ -2179,7 +2179,7 @@
         <v>3</v>
       </c>
       <c r="M20" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="21">
@@ -2230,7 +2230,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="22">
@@ -2281,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="23">
@@ -2332,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="M23" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="24">
@@ -2383,7 +2383,7 @@
         <v>3</v>
       </c>
       <c r="M24" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="25">
@@ -2434,7 +2434,7 @@
         <v>3</v>
       </c>
       <c r="M25" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="26">
@@ -2485,7 +2485,7 @@
         <v>3</v>
       </c>
       <c r="M26" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="27">
@@ -2536,7 +2536,7 @@
         <v>3</v>
       </c>
       <c r="M27" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="28">
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="M28" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="29">
@@ -2638,7 +2638,7 @@
         <v>4</v>
       </c>
       <c r="M29" s="47" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="30">
@@ -2689,7 +2689,7 @@
         <v>0</v>
       </c>
       <c r="M30" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="31">
@@ -2740,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="M31" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="32">
@@ -2791,7 +2791,7 @@
         <v>4</v>
       </c>
       <c r="M32" s="52" t="n">
-        <v>613</v>
+        <v>123384</v>
       </c>
     </row>
     <row r="33">
@@ -2842,7 +2842,7 @@
         <v>0</v>
       </c>
       <c r="M33" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="34">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="M34" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="35">
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="M35" s="41" t="n">
-        <v>378</v>
+        <v>92026</v>
       </c>
     </row>
     <row r="36">
@@ -2995,7 +2995,7 @@
         <v>0</v>
       </c>
       <c r="M36" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="37">
@@ -3046,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="M37" s="47" t="n">
-        <v>225</v>
+        <v>66610</v>
       </c>
     </row>
     <row r="38">
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="M38" s="52" t="n">
-        <v>225</v>
+        <v>66610</v>
       </c>
     </row>
     <row r="39">
@@ -3148,7 +3148,7 @@
         <v>3</v>
       </c>
       <c r="M39" s="47" t="n">
-        <v>225</v>
+        <v>66610</v>
       </c>
     </row>
     <row r="40">
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="M40" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="41">
@@ -3250,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="42">
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="43">
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="44">
@@ -3403,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="45">
@@ -3454,7 +3454,7 @@
         <v>0</v>
       </c>
       <c r="M45" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="46">
@@ -3505,7 +3505,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="47">
@@ -3556,7 +3556,7 @@
         <v>0</v>
       </c>
       <c r="M47" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="48">
@@ -3607,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="49">
@@ -3658,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="M49" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="50">
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="M50" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="51">
@@ -3760,7 +3760,7 @@
         <v>0</v>
       </c>
       <c r="M51" s="47" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="52">
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
       <c r="M52" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="53">
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="M53" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="54">
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="M54" s="52" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="55">
@@ -3964,7 +3964,7 @@
         <v>0</v>
       </c>
       <c r="M55" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="56">
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="M56" s="52" t="n">
-        <v>225</v>
+        <v>66610</v>
       </c>
     </row>
     <row r="57">
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="M57" s="47" t="n">
-        <v>263</v>
+        <v>72698</v>
       </c>
     </row>
     <row r="58">
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="M58" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="59">
@@ -4168,7 +4168,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="60">
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="M60" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="61">
@@ -4270,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="62">
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="M62" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="63">
@@ -4372,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="64">
@@ -4423,7 +4423,7 @@
         <v>0</v>
       </c>
       <c r="M64" s="52" t="n">
-        <v>263</v>
+        <v>72698</v>
       </c>
     </row>
     <row r="65">
@@ -4474,7 +4474,7 @@
         <v>6</v>
       </c>
       <c r="M65" s="47" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="66">
@@ -4525,7 +4525,7 @@
         <v>4</v>
       </c>
       <c r="M66" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="67">
@@ -4576,7 +4576,7 @@
         <v>0</v>
       </c>
       <c r="M67" s="47" t="n">
-        <v>424</v>
+        <v>64521</v>
       </c>
     </row>
     <row r="68">
@@ -4627,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="M68" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="69">
@@ -4678,7 +4678,7 @@
         <v>3</v>
       </c>
       <c r="M69" s="47" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="70">
@@ -4729,7 +4729,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="52" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="71">
@@ -4780,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="M71" s="47" t="n">
-        <v>424</v>
+        <v>64521</v>
       </c>
     </row>
     <row r="72">
@@ -4831,7 +4831,7 @@
         <v>0</v>
       </c>
       <c r="M72" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="73">
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="M73" s="47" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="74">
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="M74" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="75">
@@ -4984,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="M75" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="76">
@@ -5035,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="M76" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="77">
@@ -5086,7 +5086,7 @@
         <v>0</v>
       </c>
       <c r="M77" s="47" t="n">
-        <v>626</v>
+        <v>96504</v>
       </c>
     </row>
     <row r="78">
@@ -5137,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="M78" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="79">
@@ -5188,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="M79" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="80">
@@ -5239,7 +5239,7 @@
         <v>0</v>
       </c>
       <c r="M80" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="81">
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="82">
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="M82" s="52" t="n">
-        <v>225</v>
+        <v>66610</v>
       </c>
     </row>
     <row r="83">
@@ -5392,7 +5392,7 @@
         <v>0</v>
       </c>
       <c r="M83" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="84">
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="M84" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="85">
@@ -5494,7 +5494,7 @@
         <v>0</v>
       </c>
       <c r="M85" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="86">
@@ -5545,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="M86" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="87">
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="M87" s="47" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="88">
@@ -5647,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="89">
@@ -5698,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="M89" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="90">
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="M90" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="91">
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="M91" s="47" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="92">
@@ -5851,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="93">
@@ -5902,7 +5902,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="47" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="94">
@@ -5953,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="M94" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="95">
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="M95" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="96">
@@ -6055,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="M96" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="97">
@@ -6106,7 +6106,7 @@
         <v>0</v>
       </c>
       <c r="M97" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="98">
@@ -6157,7 +6157,7 @@
         <v>0</v>
       </c>
       <c r="M98" s="52" t="n">
-        <v>200</v>
+        <v>52804</v>
       </c>
     </row>
     <row r="99">
@@ -6208,7 +6208,7 @@
         <v>0</v>
       </c>
       <c r="M99" s="47" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="100">
@@ -6259,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="M100" s="52" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="101">
@@ -6310,7 +6310,7 @@
         <v>0</v>
       </c>
       <c r="M101" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="102">
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="M102" s="52" t="n">
-        <v>546</v>
+        <v>122852</v>
       </c>
     </row>
     <row r="103">
@@ -6412,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="M103" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="104">
@@ -6463,7 +6463,7 @@
         <v>0</v>
       </c>
       <c r="M104" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="105">
@@ -6514,7 +6514,7 @@
         <v>0</v>
       </c>
       <c r="M105" s="41" t="n">
-        <v>91</v>
+        <v>23560</v>
       </c>
     </row>
     <row r="106">
@@ -6565,7 +6565,7 @@
         <v>0</v>
       </c>
       <c r="M106" s="52" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="107">
@@ -6616,7 +6616,7 @@
         <v>3</v>
       </c>
       <c r="M107" s="47" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="108">
@@ -6667,7 +6667,7 @@
         <v>0</v>
       </c>
       <c r="M108" s="41" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="109">
@@ -6718,7 +6718,7 @@
         <v>0</v>
       </c>
       <c r="M109" s="47" t="n">
-        <v>331</v>
+        <v>88439</v>
       </c>
     </row>
     <row r="110">
@@ -6769,7 +6769,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="111">
@@ -6820,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="M111" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="112">
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="M112" s="52" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="113">
@@ -6922,7 +6922,7 @@
         <v>0</v>
       </c>
       <c r="M113" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="114">
@@ -6973,7 +6973,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="52" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="115">
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="M115" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="116">
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="M116" s="41" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="117">
@@ -7126,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="M117" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="118">
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="M118" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="119">
@@ -7228,7 +7228,7 @@
         <v>0</v>
       </c>
       <c r="M119" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="120">
@@ -7279,7 +7279,7 @@
         <v>0</v>
       </c>
       <c r="M120" s="41" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="121">
@@ -7330,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="M121" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="122">
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="M122" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="123">
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="M123" s="41" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="124">
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="M124" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="125">
@@ -7534,7 +7534,7 @@
         <v>0</v>
       </c>
       <c r="M125" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="126">
@@ -7585,7 +7585,7 @@
         <v>0</v>
       </c>
       <c r="M126" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="127">
@@ -7636,7 +7636,7 @@
         <v>0</v>
       </c>
       <c r="M127" s="47" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="128">
@@ -7687,7 +7687,7 @@
         <v>0</v>
       </c>
       <c r="M128" s="52" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="129">
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="M129" s="47" t="n">
-        <v>346</v>
+        <v>77689</v>
       </c>
     </row>
     <row r="130">
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="M130" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="131">
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="M131" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="132">
@@ -7891,7 +7891,7 @@
         <v>0</v>
       </c>
       <c r="M132" s="52" t="n">
-        <v>760</v>
+        <v>79098</v>
       </c>
     </row>
     <row r="133">
@@ -7942,7 +7942,7 @@
         <v>0</v>
       </c>
       <c r="M133" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="134">
@@ -7993,7 +7993,7 @@
         <v>0</v>
       </c>
       <c r="M134" s="52" t="n">
-        <v>480</v>
+        <v>47539</v>
       </c>
     </row>
     <row r="135">
@@ -8044,7 +8044,7 @@
         <v>0</v>
       </c>
       <c r="M135" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="136">
@@ -8095,7 +8095,7 @@
         <v>0</v>
       </c>
       <c r="M136" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="137">
@@ -8146,7 +8146,7 @@
         <v>0</v>
       </c>
       <c r="M137" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="138">
@@ -8197,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="M138" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="139">
@@ -8248,7 +8248,7 @@
         <v>0</v>
       </c>
       <c r="M139" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="140">
@@ -8299,7 +8299,7 @@
         <v>0</v>
       </c>
       <c r="M140" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="141">
@@ -8350,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="M141" s="47" t="n">
-        <v>278</v>
+        <v>42950</v>
       </c>
     </row>
     <row r="142">
@@ -8401,7 +8401,7 @@
         <v>5</v>
       </c>
       <c r="M142" s="52" t="n">
-        <v>346</v>
+        <v>77689</v>
       </c>
     </row>
     <row r="143">
@@ -8452,7 +8452,7 @@
         <v>0</v>
       </c>
       <c r="M143" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="144">
@@ -8503,7 +8503,7 @@
         <v>0</v>
       </c>
       <c r="M144" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="145">
@@ -8554,7 +8554,7 @@
         <v>0</v>
       </c>
       <c r="M145" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="146">
@@ -8605,7 +8605,7 @@
         <v>0</v>
       </c>
       <c r="M146" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="147">
@@ -8656,7 +8656,7 @@
         <v>0</v>
       </c>
       <c r="M147" s="47" t="n">
-        <v>424</v>
+        <v>64521</v>
       </c>
     </row>
     <row r="148">
@@ -8707,7 +8707,7 @@
         <v>0</v>
       </c>
       <c r="M148" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="149">
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="M149" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="150">
@@ -8809,7 +8809,7 @@
         <v>0</v>
       </c>
       <c r="M150" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="151">
@@ -8860,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="M151" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="152">
@@ -8911,7 +8911,7 @@
         <v>0</v>
       </c>
       <c r="M152" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="153">
@@ -8962,7 +8962,7 @@
         <v>0</v>
       </c>
       <c r="M153" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="154">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="M154" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="155">
@@ -9064,7 +9064,7 @@
         <v>0</v>
       </c>
       <c r="M155" s="41" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="156">
@@ -9115,7 +9115,7 @@
         <v>0</v>
       </c>
       <c r="M156" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="157">
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="M157" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="158">
@@ -9217,7 +9217,7 @@
         <v>0</v>
       </c>
       <c r="M158" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="159">
@@ -9268,7 +9268,7 @@
         <v>0</v>
       </c>
       <c r="M159" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="160">
@@ -9319,7 +9319,7 @@
         <v>3</v>
       </c>
       <c r="M160" s="52" t="n">
-        <v>263</v>
+        <v>72698</v>
       </c>
     </row>
     <row r="161">
@@ -9370,7 +9370,7 @@
         <v>0</v>
       </c>
       <c r="M161" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="162">
@@ -9421,7 +9421,7 @@
         <v>0</v>
       </c>
       <c r="M162" s="52" t="n">
-        <v>263</v>
+        <v>72698</v>
       </c>
     </row>
     <row r="163">
@@ -9472,7 +9472,7 @@
         <v>0</v>
       </c>
       <c r="M163" s="47" t="n">
-        <v>418</v>
+        <v>80854</v>
       </c>
     </row>
     <row r="164">
@@ -9523,7 +9523,7 @@
         <v>6</v>
       </c>
       <c r="M164" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="165">
@@ -9574,7 +9574,7 @@
         <v>4</v>
       </c>
       <c r="M165" s="47" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="166">
@@ -9625,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="M166" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="167">
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="M167" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="168">
@@ -9727,7 +9727,7 @@
         <v>6</v>
       </c>
       <c r="M168" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="169">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="M169" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="170">
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="M170" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="171">
@@ -9880,7 +9880,7 @@
         <v>0</v>
       </c>
       <c r="M171" s="47" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="172">
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="M172" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="173">
@@ -9982,7 +9982,7 @@
         <v>0</v>
       </c>
       <c r="M173" s="47" t="n">
-        <v>424</v>
+        <v>64521</v>
       </c>
     </row>
     <row r="174">
@@ -10033,7 +10033,7 @@
         <v>0</v>
       </c>
       <c r="M174" s="52" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="175">
@@ -10084,7 +10084,7 @@
         <v>0</v>
       </c>
       <c r="M175" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="176">
@@ -10135,7 +10135,7 @@
         <v>0</v>
       </c>
       <c r="M176" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="177">
@@ -10186,7 +10186,7 @@
         <v>0</v>
       </c>
       <c r="M177" s="47" t="n">
-        <v>264</v>
+        <v>74289</v>
       </c>
     </row>
     <row r="178">
@@ -10237,7 +10237,7 @@
         <v>0</v>
       </c>
       <c r="M178" s="52" t="n">
-        <v>264</v>
+        <v>74289</v>
       </c>
     </row>
     <row r="179">
@@ -10288,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="M179" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="180">
@@ -10339,7 +10339,7 @@
         <v>0</v>
       </c>
       <c r="M180" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="181">
@@ -10390,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="M181" s="47" t="n">
-        <v>626</v>
+        <v>96504</v>
       </c>
     </row>
     <row r="182">
@@ -10441,7 +10441,7 @@
         <v>0</v>
       </c>
       <c r="M182" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="183">
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="M183" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="184">
@@ -10543,7 +10543,7 @@
         <v>0</v>
       </c>
       <c r="M184" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="185">
@@ -10594,7 +10594,7 @@
         <v>0</v>
       </c>
       <c r="M185" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="186">
@@ -10645,7 +10645,7 @@
         <v>0</v>
       </c>
       <c r="M186" s="52" t="n">
-        <v>264</v>
+        <v>74289</v>
       </c>
     </row>
     <row r="187">
@@ -10696,7 +10696,7 @@
         <v>4</v>
       </c>
       <c r="M187" s="47" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="188">
@@ -10747,7 +10747,7 @@
         <v>0</v>
       </c>
       <c r="M188" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="189">
@@ -10798,7 +10798,7 @@
         <v>0</v>
       </c>
       <c r="M189" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="190">
@@ -10849,7 +10849,7 @@
         <v>0</v>
       </c>
       <c r="M190" s="52" t="n">
-        <v>346</v>
+        <v>77689</v>
       </c>
     </row>
     <row r="191">
@@ -10900,7 +10900,7 @@
         <v>0</v>
       </c>
       <c r="M191" s="47" t="n">
-        <v>122</v>
+        <v>32408</v>
       </c>
     </row>
     <row r="192">
@@ -10951,7 +10951,7 @@
         <v>0</v>
       </c>
       <c r="M192" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="193">
@@ -11002,7 +11002,7 @@
         <v>0</v>
       </c>
       <c r="M193" s="47" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="194">
@@ -11053,7 +11053,7 @@
         <v>5</v>
       </c>
       <c r="M194" s="52" t="n">
-        <v>346</v>
+        <v>77689</v>
       </c>
     </row>
     <row r="195">
@@ -11104,7 +11104,7 @@
         <v>0</v>
       </c>
       <c r="M195" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="196">
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="M196" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="197">
@@ -11206,7 +11206,7 @@
         <v>0</v>
       </c>
       <c r="M197" s="47" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="198">
@@ -11257,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="M198" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="199">
@@ -11308,7 +11308,7 @@
         <v>0</v>
       </c>
       <c r="M199" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="200">
@@ -11359,7 +11359,7 @@
         <v>0</v>
       </c>
       <c r="M200" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="201">
@@ -11410,7 +11410,7 @@
         <v>0</v>
       </c>
       <c r="M201" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="202">
@@ -11461,7 +11461,7 @@
         <v>0</v>
       </c>
       <c r="M202" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="203">
@@ -11512,7 +11512,7 @@
         <v>0</v>
       </c>
       <c r="M203" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="204">
@@ -11563,7 +11563,7 @@
         <v>0</v>
       </c>
       <c r="M204" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="205">
@@ -11614,7 +11614,7 @@
         <v>0</v>
       </c>
       <c r="M205" s="47" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="206">
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="M206" s="52" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="207">
@@ -11716,7 +11716,7 @@
         <v>0</v>
       </c>
       <c r="M207" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="208">
@@ -11767,7 +11767,7 @@
         <v>0</v>
       </c>
       <c r="M208" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="209">
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="M209" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="210">
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="M210" s="41" t="n">
-        <v>91</v>
+        <v>23560</v>
       </c>
     </row>
     <row r="211">
@@ -11920,7 +11920,7 @@
         <v>0</v>
       </c>
       <c r="M211" s="41" t="n">
-        <v>91</v>
+        <v>23560</v>
       </c>
     </row>
     <row r="212">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="M212" s="41" t="n">
-        <v>91</v>
+        <v>23560</v>
       </c>
     </row>
     <row r="213">
@@ -12022,7 +12022,7 @@
         <v>0</v>
       </c>
       <c r="M213" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="214">
@@ -12073,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="M214" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="215">
@@ -12124,7 +12124,7 @@
         <v>4</v>
       </c>
       <c r="M215" s="47" t="n">
-        <v>343</v>
+        <v>96138</v>
       </c>
     </row>
     <row r="216">
@@ -12175,7 +12175,7 @@
         <v>0</v>
       </c>
       <c r="M216" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="217">
@@ -12226,7 +12226,7 @@
         <v>0</v>
       </c>
       <c r="M217" s="41" t="n">
-        <v>405</v>
+        <v>61168</v>
       </c>
     </row>
     <row r="218">
@@ -12277,7 +12277,7 @@
         <v>0</v>
       </c>
       <c r="M218" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="219">
@@ -12328,7 +12328,7 @@
         <v>0</v>
       </c>
       <c r="M219" s="41" t="n">
-        <v>91</v>
+        <v>23560</v>
       </c>
     </row>
     <row r="220">
@@ -12379,7 +12379,7 @@
         <v>0</v>
       </c>
       <c r="M220" s="41" t="n">
-        <v>91</v>
+        <v>23560</v>
       </c>
     </row>
     <row r="221">
@@ -12430,7 +12430,7 @@
         <v>0</v>
       </c>
       <c r="M221" s="47" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="222">
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="M222" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="223">
@@ -12532,7 +12532,7 @@
         <v>0</v>
       </c>
       <c r="M223" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="224">
@@ -12583,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="M224" s="52" t="n">
-        <v>626</v>
+        <v>96504</v>
       </c>
     </row>
     <row r="225">
@@ -12634,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="M225" s="47" t="n">
-        <v>224</v>
+        <v>58812</v>
       </c>
     </row>
     <row r="226">
@@ -12685,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="M226" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="227">
@@ -12736,7 +12736,7 @@
         <v>0</v>
       </c>
       <c r="M227" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="228">
@@ -12787,7 +12787,7 @@
         <v>0</v>
       </c>
       <c r="M228" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="229">
@@ -12838,7 +12838,7 @@
         <v>0</v>
       </c>
       <c r="M229" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="230">
@@ -12889,7 +12889,7 @@
         <v>0</v>
       </c>
       <c r="M230" s="52" t="n">
-        <v>613</v>
+        <v>123384</v>
       </c>
     </row>
     <row r="231">
@@ -12940,7 +12940,7 @@
         <v>0</v>
       </c>
       <c r="M231" s="47" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="232">
@@ -12991,7 +12991,7 @@
         <v>0</v>
       </c>
       <c r="M232" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="233">
@@ -13042,7 +13042,7 @@
         <v>0</v>
       </c>
       <c r="M233" s="47" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="234">
@@ -13093,7 +13093,7 @@
         <v>0</v>
       </c>
       <c r="M234" s="52" t="n">
-        <v>346</v>
+        <v>77689</v>
       </c>
     </row>
     <row r="235">
@@ -13144,7 +13144,7 @@
         <v>0</v>
       </c>
       <c r="M235" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="236">
@@ -13195,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="M236" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="237">
@@ -13246,7 +13246,7 @@
         <v>0</v>
       </c>
       <c r="M237" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="238">
@@ -13297,7 +13297,7 @@
         <v>0</v>
       </c>
       <c r="M238" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="239">
@@ -13348,7 +13348,7 @@
         <v>0</v>
       </c>
       <c r="M239" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="240">
@@ -13399,7 +13399,7 @@
         <v>0</v>
       </c>
       <c r="M240" s="52" t="n">
-        <v>613</v>
+        <v>123384</v>
       </c>
     </row>
     <row r="241">
@@ -13450,7 +13450,7 @@
         <v>0</v>
       </c>
       <c r="M241" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="242">
@@ -13501,7 +13501,7 @@
         <v>0</v>
       </c>
       <c r="M242" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="243">
@@ -13552,7 +13552,7 @@
         <v>0</v>
       </c>
       <c r="M243" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="244">
@@ -13603,7 +13603,7 @@
         <v>0</v>
       </c>
       <c r="M244" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="245">
@@ -13654,7 +13654,7 @@
         <v>3</v>
       </c>
       <c r="M245" s="47" t="n">
-        <v>222</v>
+        <v>58668</v>
       </c>
     </row>
     <row r="246">
@@ -13705,7 +13705,7 @@
         <v>0</v>
       </c>
       <c r="M246" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="247">
@@ -13756,7 +13756,7 @@
         <v>0</v>
       </c>
       <c r="M247" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="248">
@@ -13807,7 +13807,7 @@
         <v>0</v>
       </c>
       <c r="M248" s="41" t="n">
-        <v>378</v>
+        <v>92026</v>
       </c>
     </row>
     <row r="249">
@@ -13858,7 +13858,7 @@
         <v>0</v>
       </c>
       <c r="M249" s="47" t="n">
-        <v>760</v>
+        <v>79098</v>
       </c>
     </row>
     <row r="250">
@@ -13909,7 +13909,7 @@
         <v>0</v>
       </c>
       <c r="M250" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="251">
@@ -13960,7 +13960,7 @@
         <v>0</v>
       </c>
       <c r="M251" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="252">
@@ -14011,7 +14011,7 @@
         <v>6</v>
       </c>
       <c r="M252" s="52" t="n">
-        <v>392</v>
+        <v>118442</v>
       </c>
     </row>
     <row r="253">
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="M253" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="254">
@@ -14113,7 +14113,7 @@
         <v>0</v>
       </c>
       <c r="M254" s="41" t="n">
-        <v>378</v>
+        <v>92026</v>
       </c>
     </row>
     <row r="255">
@@ -14164,7 +14164,7 @@
         <v>0</v>
       </c>
       <c r="M255" s="41" t="n">
-        <v>378</v>
+        <v>92026</v>
       </c>
     </row>
     <row r="256">
@@ -14215,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="M256" s="41" t="n">
-        <v>253</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="257">
@@ -14266,7 +14266,7 @@
         <v>0</v>
       </c>
       <c r="M257" s="41" t="n">
-        <v>378</v>
+        <v>92026</v>
       </c>
     </row>
     <row r="258">
@@ -14317,7 +14317,7 @@
         <v>0</v>
       </c>
       <c r="M258" s="41" t="n">
-        <v>378</v>
+        <v>92026</v>
       </c>
     </row>
     <row r="259">
@@ -14368,7 +14368,7 @@
         <v>0</v>
       </c>
       <c r="M259" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="260">
@@ -14419,7 +14419,7 @@
         <v>0</v>
       </c>
       <c r="M260" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="261">
@@ -14470,7 +14470,7 @@
         <v>0</v>
       </c>
       <c r="M261" s="47" t="n">
-        <v>480</v>
+        <v>47539</v>
       </c>
     </row>
     <row r="262">
@@ -14521,7 +14521,7 @@
         <v>0</v>
       </c>
       <c r="M262" s="52" t="n">
-        <v>480</v>
+        <v>47539</v>
       </c>
     </row>
     <row r="263">
@@ -14572,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="M263" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="264">
@@ -14623,7 +14623,7 @@
         <v>4</v>
       </c>
       <c r="M264" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="265">
@@ -14674,7 +14674,7 @@
         <v>4</v>
       </c>
       <c r="M265" s="47" t="n">
-        <v>343</v>
+        <v>96138</v>
       </c>
     </row>
     <row r="266">
@@ -14725,7 +14725,7 @@
         <v>0</v>
       </c>
       <c r="M266" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="267">
@@ -14776,7 +14776,7 @@
         <v>0</v>
       </c>
       <c r="M267" s="47" t="n">
-        <v>222</v>
+        <v>58668</v>
       </c>
     </row>
     <row r="268">
@@ -14827,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="M268" s="52" t="n">
-        <v>865</v>
+        <v>73567</v>
       </c>
     </row>
     <row r="269">
@@ -14878,7 +14878,7 @@
         <v>0</v>
       </c>
       <c r="M269" s="47" t="n">
-        <v>865</v>
+        <v>73567</v>
       </c>
     </row>
     <row r="270">
@@ -14929,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="M270" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="271">
@@ -14980,7 +14980,7 @@
         <v>0</v>
       </c>
       <c r="M271" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="272">
@@ -15031,7 +15031,7 @@
         <v>0</v>
       </c>
       <c r="M272" s="41" t="n">
-        <v>398</v>
+        <v>62533</v>
       </c>
     </row>
     <row r="273">
@@ -15082,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="M273" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="274">
@@ -15133,7 +15133,7 @@
         <v>0</v>
       </c>
       <c r="M274" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="275">
@@ -15184,7 +15184,7 @@
         <v>0</v>
       </c>
       <c r="M275" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="276">
@@ -15235,7 +15235,7 @@
         <v>4</v>
       </c>
       <c r="M276" s="52" t="n">
-        <v>538</v>
+        <v>82431</v>
       </c>
     </row>
     <row r="277">
@@ -15286,7 +15286,7 @@
         <v>0</v>
       </c>
       <c r="M277" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="278">
@@ -15337,7 +15337,7 @@
         <v>3</v>
       </c>
       <c r="M278" s="52" t="n">
-        <v>141</v>
+        <v>40143</v>
       </c>
     </row>
     <row r="279">
@@ -15388,7 +15388,7 @@
         <v>0</v>
       </c>
       <c r="M279" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="280">
@@ -15439,7 +15439,7 @@
         <v>0</v>
       </c>
       <c r="M280" s="41" t="n">
-        <v>262</v>
+        <v>73865</v>
       </c>
     </row>
     <row r="281">
@@ -15490,7 +15490,7 @@
         <v>0</v>
       </c>
       <c r="M281" s="41" t="n">
-        <v>151</v>
+        <v>43428</v>
       </c>
     </row>
     <row r="282">
@@ -15541,7 +15541,7 @@
         <v>0</v>
       </c>
       <c r="M282" s="41" t="n">
-        <v>160</v>
+        <v>47455</v>
       </c>
     </row>
     <row r="283">
@@ -15592,7 +15592,7 @@
         <v>0</v>
       </c>
       <c r="M283" s="47" t="n">
-        <v>193</v>
+        <v>43549</v>
       </c>
     </row>
     <row r="284">
@@ -15643,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="M284" s="52" t="n">
-        <v>405</v>
+        <v>113240</v>
       </c>
     </row>
     <row r="285">
@@ -15694,7 +15694,7 @@
         <v>0</v>
       </c>
       <c r="M285" s="47" t="n">
-        <v>523</v>
+        <v>147612</v>
       </c>
     </row>
     <row r="286">
@@ -15745,7 +15745,7 @@
         <v>0</v>
       </c>
       <c r="M286" s="52" t="n">
-        <v>572</v>
+        <v>161341</v>
       </c>
     </row>
     <row r="287">
@@ -15796,7 +15796,7 @@
         <v>0</v>
       </c>
       <c r="M287" s="47" t="n">
-        <v>296</v>
+        <v>78673</v>
       </c>
     </row>
     <row r="288">
@@ -15847,7 +15847,7 @@
         <v>0</v>
       </c>
       <c r="M288" s="52" t="n">
-        <v>257</v>
+        <v>68364</v>
       </c>
     </row>
     <row r="289">
@@ -15898,7 +15898,7 @@
         <v>0</v>
       </c>
       <c r="M289" s="47" t="n">
-        <v>257</v>
+        <v>68364</v>
       </c>
     </row>
     <row r="290">
@@ -15949,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="M290" s="52" t="n">
-        <v>257</v>
+        <v>68364</v>
       </c>
     </row>
     <row r="291">
@@ -16000,7 +16000,7 @@
         <v>0</v>
       </c>
       <c r="M291" s="47" t="n">
-        <v>264</v>
+        <v>70175</v>
       </c>
     </row>
     <row r="292">
@@ -16051,7 +16051,7 @@
         <v>0</v>
       </c>
       <c r="M292" s="52" t="n">
-        <v>453</v>
+        <v>8165</v>
       </c>
     </row>
     <row r="293">
@@ -16102,7 +16102,7 @@
         <v>0</v>
       </c>
       <c r="M293" s="47" t="n">
-        <v>359</v>
+        <v>100539</v>
       </c>
     </row>
     <row r="294">
@@ -16153,7 +16153,7 @@
         <v>0</v>
       </c>
       <c r="M294" s="52" t="n">
-        <v>296</v>
+        <v>78673</v>
       </c>
     </row>
     <row r="295">
@@ -16204,7 +16204,7 @@
         <v>0</v>
       </c>
       <c r="M295" s="47" t="n">
-        <v>296</v>
+        <v>78673</v>
       </c>
     </row>
     <row r="296">
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="M296" s="52" t="n">
-        <v>296</v>
+        <v>78673</v>
       </c>
     </row>
     <row r="297">
@@ -16306,7 +16306,7 @@
         <v>0</v>
       </c>
       <c r="M297" s="47" t="n">
-        <v>296</v>
+        <v>78673</v>
       </c>
     </row>
     <row r="298">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="M298" s="52" t="n">
-        <v>284</v>
+        <v>75377</v>
       </c>
     </row>
     <row r="299">
@@ -16408,7 +16408,7 @@
         <v>0</v>
       </c>
       <c r="M299" s="47" t="n">
-        <v>325</v>
+        <v>91411</v>
       </c>
     </row>
     <row r="300">
@@ -16459,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="M300" s="52" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="301">
@@ -16510,7 +16510,7 @@
         <v>0</v>
       </c>
       <c r="M301" s="47" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="302">
@@ -16561,7 +16561,7 @@
         <v>0</v>
       </c>
       <c r="M302" s="52" t="n">
-        <v>368</v>
+        <v>103093</v>
       </c>
     </row>
     <row r="303">
@@ -16612,7 +16612,7 @@
         <v>0</v>
       </c>
       <c r="M303" s="47" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="304">
@@ -16663,7 +16663,7 @@
         <v>0</v>
       </c>
       <c r="M304" s="52" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="305">
@@ -16714,7 +16714,7 @@
         <v>0</v>
       </c>
       <c r="M305" s="47" t="n">
-        <v>299</v>
+        <v>83836</v>
       </c>
     </row>
     <row r="306">
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="M306" s="52" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="307">
@@ -16816,7 +16816,7 @@
         <v>0</v>
       </c>
       <c r="M307" s="47" t="n">
-        <v>366</v>
+        <v>102232</v>
       </c>
     </row>
     <row r="308">
@@ -16867,7 +16867,7 @@
         <v>0</v>
       </c>
       <c r="M308" s="52" t="n">
-        <v>366</v>
+        <v>102232</v>
       </c>
     </row>
     <row r="309">
@@ -16918,7 +16918,7 @@
         <v>0</v>
       </c>
       <c r="M309" s="47" t="n">
-        <v>368</v>
+        <v>103093</v>
       </c>
     </row>
     <row r="310">
@@ -16969,7 +16969,7 @@
         <v>0</v>
       </c>
       <c r="M310" s="52" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="311">
@@ -17020,7 +17020,7 @@
         <v>0</v>
       </c>
       <c r="M311" s="47" t="n">
-        <v>401</v>
+        <v>112524</v>
       </c>
     </row>
     <row r="312">
@@ -17071,7 +17071,7 @@
         <v>0</v>
       </c>
       <c r="M312" s="52" t="n">
-        <v>223</v>
+        <v>58925</v>
       </c>
     </row>
     <row r="313">
@@ -17122,7 +17122,7 @@
         <v>0</v>
       </c>
       <c r="M313" s="47" t="n">
-        <v>366</v>
+        <v>102232</v>
       </c>
     </row>
     <row r="314">
@@ -17173,7 +17173,7 @@
         <v>0</v>
       </c>
       <c r="M314" s="52" t="n">
-        <v>914</v>
+        <v>170188</v>
       </c>
     </row>
     <row r="315">
@@ -17224,7 +17224,7 @@
         <v>0</v>
       </c>
       <c r="M315" s="47" t="n">
-        <v>1280</v>
+        <v>33298</v>
       </c>
     </row>
     <row r="316">
@@ -17275,7 +17275,7 @@
         <v>0</v>
       </c>
       <c r="M316" s="52" t="n">
-        <v>430</v>
+        <v>98975</v>
       </c>
     </row>
     <row r="317">
@@ -17326,7 +17326,7 @@
         <v>0</v>
       </c>
       <c r="M317" s="47" t="n">
-        <v>1516</v>
+        <v>39417</v>
       </c>
     </row>
     <row r="318">
@@ -17377,7 +17377,7 @@
         <v>0</v>
       </c>
       <c r="M318" s="52" t="n">
-        <v>343</v>
+        <v>96645</v>
       </c>
     </row>
     <row r="319">
@@ -17428,7 +17428,7 @@
         <v>0</v>
       </c>
       <c r="M319" s="47" t="n">
-        <v>668</v>
+        <v>101613</v>
       </c>
     </row>
     <row r="320">
@@ -17479,7 +17479,7 @@
         <v>0</v>
       </c>
       <c r="M320" s="52" t="n">
-        <v>4278</v>
+        <v>119785</v>
       </c>
     </row>
     <row r="321">
@@ -17530,7 +17530,7 @@
         <v>0</v>
       </c>
       <c r="M321" s="47" t="n">
-        <v>1776</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="322">
@@ -17581,7 +17581,7 @@
         <v>0</v>
       </c>
       <c r="M322" s="52" t="n">
-        <v>484</v>
+        <v>114293</v>
       </c>
     </row>
     <row r="323">
@@ -17632,7 +17632,7 @@
         <v>0</v>
       </c>
       <c r="M323" s="47" t="n">
-        <v>736</v>
+        <v>111959</v>
       </c>
     </row>
     <row r="324">
@@ -17683,7 +17683,7 @@
         <v>0</v>
       </c>
       <c r="M324" s="52" t="n">
-        <v>152</v>
+        <v>17652</v>
       </c>
     </row>
     <row r="325">
@@ -17734,7 +17734,7 @@
         <v>0</v>
       </c>
       <c r="M325" s="47" t="n">
-        <v>601</v>
+        <v>94458</v>
       </c>
     </row>
     <row r="326">
@@ -17785,7 +17785,7 @@
         <v>0</v>
       </c>
       <c r="M326" s="52" t="n">
-        <v>784</v>
+        <v>152128</v>
       </c>
     </row>
     <row r="327">
@@ -17836,7 +17836,7 @@
         <v>0</v>
       </c>
       <c r="M327" s="47" t="n">
-        <v>701</v>
+        <v>125528</v>
       </c>
     </row>
     <row r="328">
@@ -17887,7 +17887,7 @@
         <v>0</v>
       </c>
       <c r="M328" s="52" t="n">
-        <v>788</v>
+        <v>127759</v>
       </c>
     </row>
     <row r="329">
@@ -17938,7 +17938,7 @@
         <v>0</v>
       </c>
       <c r="M329" s="47" t="n">
-        <v>2398</v>
+        <v>81554</v>
       </c>
     </row>
     <row r="330">
@@ -17989,7 +17989,7 @@
         <v>0</v>
       </c>
       <c r="M330" s="52" t="n">
-        <v>159</v>
+        <v>42363</v>
       </c>
     </row>
     <row r="331">
@@ -18040,7 +18040,7 @@
         <v>0</v>
       </c>
       <c r="M331" s="47" t="n">
-        <v>598</v>
+        <v>87331</v>
       </c>
     </row>
     <row r="332">
@@ -18091,7 +18091,7 @@
         <v>0</v>
       </c>
       <c r="M332" s="52" t="n">
-        <v>783</v>
+        <v>119919</v>
       </c>
     </row>
     <row r="333">
@@ -18142,7 +18142,7 @@
         <v>0</v>
       </c>
       <c r="M333" s="47" t="n">
-        <v>918</v>
+        <v>140491</v>
       </c>
     </row>
     <row r="334">
@@ -18193,7 +18193,7 @@
         <v>0</v>
       </c>
       <c r="M334" s="52" t="n">
-        <v>2283</v>
+        <v>73084</v>
       </c>
     </row>
     <row r="335">
@@ -18244,7 +18244,7 @@
         <v>0</v>
       </c>
       <c r="M335" s="47" t="n">
-        <v>2855</v>
+        <v>97093</v>
       </c>
     </row>
     <row r="336">
@@ -18295,7 +18295,7 @@
         <v>0</v>
       </c>
       <c r="M336" s="52" t="n">
-        <v>4263</v>
+        <v>115125</v>
       </c>
     </row>
     <row r="337">
@@ -18346,7 +18346,7 @@
         <v>0</v>
       </c>
       <c r="M337" s="47" t="n">
-        <v>864</v>
+        <v>131341</v>
       </c>
     </row>
     <row r="338">
@@ -18397,7 +18397,7 @@
         <v>0</v>
       </c>
       <c r="M338" s="52" t="n">
-        <v>3526</v>
+        <v>112839</v>
       </c>
     </row>
     <row r="339">
@@ -18448,7 +18448,7 @@
         <v>0</v>
       </c>
       <c r="M339" s="47" t="n">
-        <v>1768</v>
+        <v>120242</v>
       </c>
     </row>
     <row r="340">
@@ -18499,7 +18499,7 @@
         <v>0</v>
       </c>
       <c r="M340" s="52" t="n">
-        <v>1736</v>
+        <v>118108</v>
       </c>
     </row>
     <row r="341">
@@ -18550,7 +18550,7 @@
         <v>0</v>
       </c>
       <c r="M341" s="47" t="n">
-        <v>3201</v>
+        <v>108838</v>
       </c>
     </row>
     <row r="342">
@@ -18601,7 +18601,7 @@
         <v>0</v>
       </c>
       <c r="M342" s="52" t="n">
-        <v>511</v>
+        <v>65968</v>
       </c>
     </row>
     <row r="343">
@@ -18652,7 +18652,7 @@
         <v>0</v>
       </c>
       <c r="M343" s="47" t="n">
-        <v>1776</v>
+        <v>46176</v>
       </c>
     </row>
   </sheetData>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO_Pretty.xlsx
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B2" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C2" s="37" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B3" s="30" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C3" s="43" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C5" s="43" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ GADOORA</t>
+          <t>Soura to Gadoora</t>
         </is>
       </c>
       <c r="C6" s="43" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C7" s="43" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B8" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C8" s="43" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C9" s="43" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ SOURA</t>
+          <t>Jehangir Chowk to Soura</t>
         </is>
       </c>
       <c r="C10" s="43" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C11" s="37" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C12" s="37" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="B13" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C13" s="53" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C14" s="43" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C15" s="37" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B16" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C16" s="43" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C17" s="37" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="B18" s="29" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C18" s="43" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C19" s="43" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="B20" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C20" s="43" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C21" s="37" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B22" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C22" s="37" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C23" s="37" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="B24" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C25" s="43" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B26" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C26" s="43" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B27" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C27" s="43" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>SORA ↔ PARIMPORA</t>
+          <t>Sora to Parimpora</t>
         </is>
       </c>
       <c r="C28" s="37" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B29" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C29" s="43" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C30" s="37" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C31" s="37" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="B32" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C32" s="43" t="inlineStr">
@@ -2802,7 +2802,7 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C33" s="37" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>SORA ↔ LD</t>
+          <t>Sora to LD</t>
         </is>
       </c>
       <c r="C34" s="37" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C35" s="37" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B36" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C36" s="43" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B37" s="30" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C37" s="43" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C38" s="43" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B39" s="30" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C39" s="43" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C40" s="37" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ QAMARWARI</t>
+          <t>Lalbazar to Qamarwari</t>
         </is>
       </c>
       <c r="C41" s="43" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="B42" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C42" s="53" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C43" s="37" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ QAMARWARI</t>
+          <t>Soura to Qamarwari</t>
         </is>
       </c>
       <c r="C44" s="37" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C45" s="37" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C46" s="37" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C47" s="37" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C48" s="37" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C49" s="37" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B50" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C50" s="43" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="B51" s="30" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C51" s="43" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C52" s="37" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C53" s="37" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="B54" s="29" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C54" s="43" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B55" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C55" s="43" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B56" s="29" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="B57" s="30" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C57" s="43" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B58" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C58" s="43" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="B59" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C59" s="43" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="B60" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C60" s="43" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="B61" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C61" s="43" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B62" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C62" s="43" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="B63" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C63" s="43" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B64" s="29" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ HAZRATBAL</t>
+          <t>Qamarwari to Hazratbal</t>
         </is>
       </c>
       <c r="C64" s="43" t="inlineStr">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="B65" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C65" s="43" t="inlineStr">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="B66" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C66" s="43" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="B67" s="30" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C67" s="43" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="B68" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C68" s="43" t="inlineStr">
@@ -4638,7 +4638,7 @@
       </c>
       <c r="B69" s="30" t="inlineStr">
         <is>
-          <t>SAIDAKADAL ↔ BYPASS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="C69" s="43" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>SAIDAKADAL ↔ BYPASS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="C70" s="43" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="B71" s="30" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C71" s="43" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="B72" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C72" s="43" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="B73" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C73" s="43" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="B74" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C74" s="37" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C75" s="37" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B76" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C76" s="43" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="B77" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C77" s="43" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="B78" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C78" s="37" t="inlineStr">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C79" s="37" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="B80" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C80" s="37" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C81" s="37" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="B82" s="29" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="C82" s="43" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B83" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C83" s="43" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="B84" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C84" s="43" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B85" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C85" s="43" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="B86" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="C86" s="43" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="B87" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C87" s="43" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="B88" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C88" s="43" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="B89" s="23" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ JEHANGIR CHOWK</t>
+          <t>Qamarwari to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C89" s="37" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="B90" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C90" s="53" t="inlineStr">
@@ -5760,7 +5760,7 @@
       </c>
       <c r="B91" s="30" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C91" s="43" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B92" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JEHANGIR CHOWK</t>
+          <t>Parimpora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C92" s="37" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B93" s="30" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C93" s="43" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="B94" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C94" s="43" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="B95" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C95" s="43" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="B96" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C96" s="43" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B97" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C97" s="43" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B98" s="29" t="inlineStr">
         <is>
-          <t>JVC ↔ BATWARA</t>
+          <t>JVC to Batwara</t>
         </is>
       </c>
       <c r="C98" s="43" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="B99" s="30" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C99" s="53" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="B100" s="29" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C100" s="43" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="B101" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="B102" s="29" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ BONE JOINT HOSPITAL BARZALLA</t>
+          <t>Hazratbal to Bone Joint Hospital Barzalla</t>
         </is>
       </c>
       <c r="C102" s="53" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="B103" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="B104" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B105" s="23" t="inlineStr">
         <is>
-          <t>GBS ↔ LAL CHOWK</t>
+          <t>GBS to LAL Chowk</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="B106" s="29" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="C106" s="53" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="B107" s="30" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C107" s="43" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="B108" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="C108" s="37" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B109" s="30" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ BAGHI MEHTAB</t>
+          <t>Qamarwari to Baghi Mehtab</t>
         </is>
       </c>
       <c r="C109" s="43" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="B110" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C110" s="43" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="B111" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C111" s="43" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="B112" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C112" s="43" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="B113" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="B114" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C114" s="53" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="B115" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C115" s="37" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="B116" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C116" s="37" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="B117" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C117" s="37" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="B118" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C118" s="37" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B119" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C119" s="37" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="B120" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C120" s="37" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="B121" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C121" s="37" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="B122" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C122" s="37" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="B123" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C123" s="37" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="B124" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C124" s="37" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="B125" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C125" s="37" t="inlineStr">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="B126" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C126" s="37" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="B127" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C127" s="43" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="B128" s="29" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="C128" s="43" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="B129" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C129" s="43" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="B130" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C130" s="37" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C131" s="37" t="inlineStr">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B132" s="29" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="C132" s="43" t="inlineStr">
@@ -7902,7 +7902,7 @@
       </c>
       <c r="B133" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C133" s="37" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="B134" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C134" s="43" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="B135" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C135" s="43" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="B136" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C136" s="43" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="B137" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C137" s="43" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="B138" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C138" s="43" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="B139" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C139" s="37" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="B140" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C140" s="37" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="B141" s="30" t="inlineStr">
         <is>
-          <t>BATMALOO ↔ DALGATE</t>
+          <t>Batmaloo to Dalgate</t>
         </is>
       </c>
       <c r="C141" s="43" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="B142" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C142" s="43" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="B143" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C143" s="37" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="B144" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C144" s="43" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="B145" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C145" s="37" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="B146" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C146" s="37" t="inlineStr">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="B147" s="30" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C147" s="43" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="B148" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C148" s="53" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="B149" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C149" s="37" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="B150" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C150" s="37" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="B151" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C151" s="43" t="inlineStr">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="B152" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C152" s="37" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="B153" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C153" s="37" t="inlineStr">
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B154" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C154" s="37" t="inlineStr">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="B155" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C155" s="37" t="inlineStr">
@@ -9075,7 +9075,7 @@
       </c>
       <c r="B156" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C156" s="37" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="B157" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C157" s="37" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="B158" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C158" s="37" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="B159" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C159" s="37" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="B160" s="29" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C160" s="43" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="B161" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C161" s="37" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="B162" s="29" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="C162" s="43" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="B163" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ DALGATE</t>
+          <t>Soura to Dalgate</t>
         </is>
       </c>
       <c r="C163" s="53" t="inlineStr">
@@ -9483,7 +9483,7 @@
       </c>
       <c r="B164" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C164" s="43" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="B165" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C165" s="43" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="B166" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C166" s="37" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B167" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C167" s="37" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="B168" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C168" s="43" t="inlineStr">
@@ -9738,7 +9738,7 @@
       </c>
       <c r="B169" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C169" s="37" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="B170" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ CHUNTWALIWAR</t>
+          <t>Soura to Chuntwaliwar</t>
         </is>
       </c>
       <c r="C170" s="37" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="B171" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C171" s="43" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B172" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C172" s="43" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="B173" s="30" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C173" s="43" t="inlineStr">
@@ -9993,7 +9993,7 @@
       </c>
       <c r="B174" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ BATAMALLO</t>
+          <t>Soura to Batamallo</t>
         </is>
       </c>
       <c r="C174" s="53" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="B175" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C175" s="37" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="B176" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C176" s="37" t="inlineStr">
@@ -10146,7 +10146,7 @@
       </c>
       <c r="B177" s="30" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C177" s="43" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="B178" s="29" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C178" s="43" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="B179" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C179" s="37" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B180" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C180" s="37" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="B181" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C181" s="43" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="B182" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C182" s="37" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="B183" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C183" s="43" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="B184" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C184" s="53" t="inlineStr">
@@ -10554,7 +10554,7 @@
       </c>
       <c r="B185" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C185" s="43" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B186" s="29" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="C186" s="43" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="B187" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C187" s="43" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="B188" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C188" s="43" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="B189" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C189" s="37" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="B190" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C190" s="43" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="B191" s="30" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ DALGATE</t>
+          <t>Rangpora to Dalgate</t>
         </is>
       </c>
       <c r="C191" s="43" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="B192" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C192" s="37" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="B193" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C193" s="43" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B194" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C194" s="43" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="B195" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C195" s="37" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="B196" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C196" s="53" t="inlineStr">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B197" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C197" s="43" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="B198" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C198" s="43" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="B199" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C199" s="37" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="B200" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C200" s="53" t="inlineStr">
@@ -11370,7 +11370,7 @@
       </c>
       <c r="B201" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C201" s="37" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="B202" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C202" s="37" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="B203" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="C203" s="37" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="B204" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C204" s="43" t="inlineStr">
@@ -11574,7 +11574,7 @@
       </c>
       <c r="B205" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C205" s="43" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="B206" s="29" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C206" s="53" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="B207" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C207" s="37" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="B208" s="23" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C208" s="37" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="B209" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C209" s="37" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="B210" s="23" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C210" s="37" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B211" s="23" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C211" s="37" t="inlineStr">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="B212" s="23" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C212" s="37" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="B213" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C213" s="37" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="B214" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C214" s="43" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="B215" s="30" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C215" s="43" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="B216" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C216" s="37" t="inlineStr">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="B217" s="23" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="C217" s="37" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="B218" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="C218" s="43" t="inlineStr">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="B219" s="23" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C219" s="37" t="inlineStr">
@@ -12339,7 +12339,7 @@
       </c>
       <c r="B220" s="23" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="C220" s="37" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="B221" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C221" s="43" t="inlineStr">
@@ -12441,7 +12441,7 @@
       </c>
       <c r="B222" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C222" s="37" t="inlineStr">
@@ -12492,7 +12492,7 @@
       </c>
       <c r="B223" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C223" s="43" t="inlineStr">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="B224" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="C224" s="43" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="B225" s="30" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="C225" s="43" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="B226" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C226" s="37" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B227" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C227" s="37" t="inlineStr">
@@ -12747,7 +12747,7 @@
       </c>
       <c r="B228" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C228" s="37" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B229" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C229" s="37" t="inlineStr">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="B230" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C230" s="43" t="inlineStr">
@@ -12900,7 +12900,7 @@
       </c>
       <c r="B231" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C231" s="43" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="B232" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C232" s="43" t="inlineStr">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="B233" s="30" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C233" s="53" t="inlineStr">
@@ -13053,7 +13053,7 @@
       </c>
       <c r="B234" s="29" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="C234" s="43" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="B235" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C235" s="37" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="B236" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C236" s="43" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="B237" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C237" s="37" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="B238" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C238" s="37" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="B239" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C239" s="37" t="inlineStr">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="B240" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="C240" s="43" t="inlineStr">
@@ -13410,7 +13410,7 @@
       </c>
       <c r="B241" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C241" s="37" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="B242" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C242" s="37" t="inlineStr">
@@ -13512,7 +13512,7 @@
       </c>
       <c r="B243" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C243" s="37" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="B244" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C244" s="37" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B245" s="30" t="inlineStr">
         <is>
-          <t>MA ROAD ↔ SAFAKADAL</t>
+          <t>Ma Road to Safakadal</t>
         </is>
       </c>
       <c r="C245" s="43" t="inlineStr">
@@ -13665,7 +13665,7 @@
       </c>
       <c r="B246" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C246" s="37" t="inlineStr">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="B247" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C247" s="37" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="B248" s="23" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C248" s="37" t="inlineStr">
@@ -13818,7 +13818,7 @@
       </c>
       <c r="B249" s="30" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="C249" s="43" t="inlineStr">
@@ -13869,7 +13869,7 @@
       </c>
       <c r="B250" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C250" s="37" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="B251" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C251" s="37" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B252" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C252" s="43" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="B253" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C253" s="37" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="B254" s="23" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C254" s="37" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="B255" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LALCHOWK</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="C255" s="37" t="inlineStr">
@@ -14175,7 +14175,7 @@
       </c>
       <c r="B256" s="23" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="C256" s="37" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="B257" s="23" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="C257" s="37" t="inlineStr">
@@ -14277,7 +14277,7 @@
       </c>
       <c r="B258" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LALCHOWK</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="C258" s="37" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="B259" s="23" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C259" s="37" t="inlineStr">
@@ -14379,7 +14379,7 @@
       </c>
       <c r="B260" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C260" s="37" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="B261" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C261" s="43" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="B262" s="29" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="C262" s="43" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="B263" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C263" s="37" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="B264" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C264" s="43" t="inlineStr">
@@ -14634,7 +14634,7 @@
       </c>
       <c r="B265" s="30" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="C265" s="43" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="B266" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C266" s="43" t="inlineStr">
@@ -14736,7 +14736,7 @@
       </c>
       <c r="B267" s="30" t="inlineStr">
         <is>
-          <t>MA ROAD ↔ PARIMPORA</t>
+          <t>Ma Road to Parimpora</t>
         </is>
       </c>
       <c r="C267" s="43" t="inlineStr">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="B268" s="29" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C268" s="43" t="inlineStr">
@@ -14838,7 +14838,7 @@
       </c>
       <c r="B269" s="30" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="C269" s="43" t="inlineStr">
@@ -14889,7 +14889,7 @@
       </c>
       <c r="B270" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C270" s="37" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="B271" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C271" s="37" t="inlineStr">
@@ -14991,7 +14991,7 @@
       </c>
       <c r="B272" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="C272" s="37" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="B273" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C273" s="37" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="B274" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C274" s="37" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="B275" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C275" s="37" t="inlineStr">
@@ -15195,7 +15195,7 @@
       </c>
       <c r="B276" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="C276" s="43" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="B277" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C277" s="37" t="inlineStr">
@@ -15297,7 +15297,7 @@
       </c>
       <c r="B278" s="29" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="C278" s="43" t="inlineStr">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="B279" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C279" s="37" t="inlineStr">
@@ -15399,7 +15399,7 @@
       </c>
       <c r="B280" s="23" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="C280" s="37" t="inlineStr">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="B281" s="23" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="C281" s="37" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="B282" s="23" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="C282" s="37" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="B283" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to SHANGLIPORA</t>
+          <t>Srinagar to Shanglipora</t>
         </is>
       </c>
       <c r="C283" s="43" t="inlineStr">
@@ -15603,7 +15603,7 @@
       </c>
       <c r="B284" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHEWDARA</t>
+          <t>Srinagar to Chewdara</t>
         </is>
       </c>
       <c r="C284" s="43" t="inlineStr">
@@ -15654,7 +15654,7 @@
       </c>
       <c r="B285" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHOWKIBAL</t>
+          <t>Srinagar to Chowkibal</t>
         </is>
       </c>
       <c r="C285" s="53" t="inlineStr">
@@ -15705,7 +15705,7 @@
       </c>
       <c r="B286" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to SAFAPORA SUMBAL</t>
+          <t>Srinagar to Safapora Sumbal</t>
         </is>
       </c>
       <c r="C286" s="43" t="inlineStr">
@@ -15756,7 +15756,7 @@
       </c>
       <c r="B287" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to URI BARAMULLA</t>
+          <t>Srinagar to URI Baramulla</t>
         </is>
       </c>
       <c r="C287" s="43" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="B288" s="29" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C288" s="43" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="B289" s="30" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C289" s="43" t="inlineStr">
@@ -15909,7 +15909,7 @@
       </c>
       <c r="B290" s="29" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="C290" s="43" t="inlineStr">
@@ -15960,7 +15960,7 @@
       </c>
       <c r="B291" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to BANDIPORA</t>
+          <t>Srinagar to Bandipora</t>
         </is>
       </c>
       <c r="C291" s="43" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B292" s="29" t="inlineStr">
         <is>
-          <t>BANDIPORA to BARAMULLA</t>
+          <t>Bandipora to Baramulla</t>
         </is>
       </c>
       <c r="C292" s="53" t="inlineStr">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="B293" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to ZALOORA</t>
+          <t>Srinagar to Zaloora</t>
         </is>
       </c>
       <c r="C293" s="43" t="inlineStr">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="B294" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to BARAMULLA</t>
+          <t>Srinagar to Baramulla</t>
         </is>
       </c>
       <c r="C294" s="43" t="inlineStr">
@@ -16164,7 +16164,7 @@
       </c>
       <c r="B295" s="30" t="inlineStr">
         <is>
-          <t>KAMALKOTE to BARAMULLA</t>
+          <t>Kamalkote to Baramulla</t>
         </is>
       </c>
       <c r="C295" s="53" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="B296" s="29" t="inlineStr">
         <is>
-          <t>GARKOTE to BARAMULLA</t>
+          <t>Garkote to Baramulla</t>
         </is>
       </c>
       <c r="C296" s="53" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="B297" s="30" t="inlineStr">
         <is>
-          <t>NAMBIA to BARAMULLA</t>
+          <t>Nambia to Baramulla</t>
         </is>
       </c>
       <c r="C297" s="53" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="B298" s="29" t="inlineStr">
         <is>
-          <t>BARAMULA to KUPWRA</t>
+          <t>Baramula to Kupwra</t>
         </is>
       </c>
       <c r="C298" s="43" t="inlineStr">
@@ -16368,7 +16368,7 @@
       </c>
       <c r="B299" s="30" t="inlineStr">
         <is>
-          <t>HARMAN to SRINAGAR</t>
+          <t>Harman to Srinagar</t>
         </is>
       </c>
       <c r="C299" s="43" t="inlineStr">
@@ -16419,7 +16419,7 @@
       </c>
       <c r="B300" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to BY PASS</t>
+          <t>Srinagar to By Pass</t>
         </is>
       </c>
       <c r="C300" s="43" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="B301" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C301" s="43" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="B302" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to GULABAGH</t>
+          <t>Srinagar to Gulabagh</t>
         </is>
       </c>
       <c r="C302" s="43" t="inlineStr">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="B303" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C303" s="43" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B304" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C304" s="43" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="B305" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to BUCHPORA</t>
+          <t>Srinagar to Buchpora</t>
         </is>
       </c>
       <c r="C305" s="43" t="inlineStr">
@@ -16725,7 +16725,7 @@
       </c>
       <c r="B306" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C306" s="43" t="inlineStr">
@@ -16776,7 +16776,7 @@
       </c>
       <c r="B307" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C307" s="43" t="inlineStr">
@@ -16827,7 +16827,7 @@
       </c>
       <c r="B308" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C308" s="43" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="B309" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to GULABAGH</t>
+          <t>Srinagar to Gulabagh</t>
         </is>
       </c>
       <c r="C309" s="43" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="B310" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C310" s="43" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="B311" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to GANDERBAL</t>
+          <t>Srinagar to Ganderbal</t>
         </is>
       </c>
       <c r="C311" s="43" t="inlineStr">
@@ -17031,7 +17031,7 @@
       </c>
       <c r="B312" s="29" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="C312" s="43" t="inlineStr">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="B313" s="30" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="C313" s="43" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="B331" s="30" t="inlineStr">
         <is>
-          <t>JKPDC Jehangir Chowk to Wadwan</t>
+          <t>Jkpdc Jehangir Chowk to Wadwan</t>
         </is>
       </c>
       <c r="C331" s="53" t="inlineStr">
@@ -18612,7 +18612,7 @@
       </c>
       <c r="B343" s="30" t="inlineStr">
         <is>
-          <t>Batamaloo to DC Office Budgam</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="C343" s="53" t="inlineStr">

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO_Pretty.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO_Pretty.xlsx
@@ -840,7 +840,7 @@
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Engine v3.3.7  ·  Generated 30 May 2026  ·  Phase-1 Conservative plan  ·  35-min headway ceiling</t>
+          <t>Engine v3.3.7  ·  Generated 03 Jun 2026  ·  Phase-1 Conservative plan  ·  35-min headway ceiling</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
     <row r="2">
       <c r="A2" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B2" s="23" t="inlineStr">
@@ -1369,7 +1369,7 @@
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B5" s="30" t="inlineStr">
@@ -1420,7 +1420,7 @@
     <row r="6">
       <c r="A6" s="48" t="inlineStr">
         <is>
-          <t>PWGB08051203</t>
+          <t>SRGB10055803</t>
         </is>
       </c>
       <c r="B6" s="29" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="7">
       <c r="A7" s="42" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B7" s="30" t="inlineStr">
@@ -1522,7 +1522,7 @@
     <row r="8">
       <c r="A8" s="48" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B8" s="29" t="inlineStr">
@@ -1573,7 +1573,7 @@
     <row r="9">
       <c r="A9" s="42" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -1624,7 +1624,7 @@
     <row r="10">
       <c r="A10" s="48" t="inlineStr">
         <is>
-          <t>SRPW10082512</t>
+          <t>SRSR10102558</t>
         </is>
       </c>
       <c r="B10" s="29" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="11">
       <c r="A11" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B11" s="23" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="12">
       <c r="A12" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B12" s="23" t="inlineStr">
@@ -1777,7 +1777,7 @@
     <row r="13">
       <c r="A13" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -1879,7 +1879,7 @@
     <row r="15">
       <c r="A15" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B15" s="23" t="inlineStr">
@@ -1930,7 +1930,7 @@
     <row r="16">
       <c r="A16" s="48" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B16" s="29" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="17">
       <c r="A17" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B17" s="23" t="inlineStr">
@@ -2032,7 +2032,7 @@
     <row r="18">
       <c r="A18" s="48" t="inlineStr">
         <is>
-          <t>KWSP07090815</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B18" s="29" t="inlineStr">
@@ -2083,7 +2083,7 @@
     <row r="19">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
@@ -2134,7 +2134,7 @@
     <row r="20">
       <c r="A20" s="48" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B20" s="29" t="inlineStr">
@@ -2185,7 +2185,7 @@
     <row r="21">
       <c r="A21" s="36" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B21" s="23" t="inlineStr">
@@ -2236,7 +2236,7 @@
     <row r="22">
       <c r="A22" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -2287,7 +2287,7 @@
     <row r="23">
       <c r="A23" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B23" s="23" t="inlineStr">
@@ -2338,7 +2338,7 @@
     <row r="24">
       <c r="A24" s="48" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B24" s="29" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="25">
       <c r="A25" s="42" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="27">
       <c r="A27" s="42" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="30">
       <c r="A30" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B30" s="23" t="inlineStr">
@@ -2695,7 +2695,7 @@
     <row r="31">
       <c r="A31" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="32">
       <c r="A32" s="48" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B32" s="29" t="inlineStr">
@@ -2797,7 +2797,7 @@
     <row r="33">
       <c r="A33" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="34">
       <c r="A34" s="36" t="inlineStr">
         <is>
-          <t>SRSP10095015</t>
+          <t>SRSR10105060</t>
         </is>
       </c>
       <c r="B34" s="23" t="inlineStr">
@@ -2899,7 +2899,7 @@
     <row r="35">
       <c r="A35" s="36" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B35" s="23" t="inlineStr">
@@ -2950,7 +2950,7 @@
     <row r="36">
       <c r="A36" s="48" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B36" s="29" t="inlineStr">
@@ -3154,7 +3154,7 @@
     <row r="40">
       <c r="A40" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B40" s="23" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="43">
       <c r="A43" s="36" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">
@@ -3358,7 +3358,7 @@
     <row r="44">
       <c r="A44" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101206</t>
+          <t>SRSR10105806</t>
         </is>
       </c>
       <c r="B44" s="23" t="inlineStr">
@@ -3562,7 +3562,7 @@
     <row r="48">
       <c r="A48" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B48" s="23" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="50">
       <c r="A50" s="48" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B50" s="29" t="inlineStr">
@@ -3766,7 +3766,7 @@
     <row r="52">
       <c r="A52" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B52" s="23" t="inlineStr">
@@ -3817,7 +3817,7 @@
     <row r="53">
       <c r="A53" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B53" s="23" t="inlineStr">
@@ -4429,7 +4429,7 @@
     <row r="65">
       <c r="A65" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B65" s="30" t="inlineStr">
@@ -4633,7 +4633,7 @@
     <row r="69">
       <c r="A69" s="42" t="inlineStr">
         <is>
-          <t>SPGB09052002</t>
+          <t>SRGB10056102</t>
         </is>
       </c>
       <c r="B69" s="30" t="inlineStr">
@@ -4684,7 +4684,7 @@
     <row r="70">
       <c r="A70" s="48" t="inlineStr">
         <is>
-          <t>SPGB09052002</t>
+          <t>SRGB10056102</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="83">
       <c r="A83" s="42" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B83" s="30" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="87">
       <c r="A87" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B87" s="30" t="inlineStr">
@@ -5602,7 +5602,7 @@
     <row r="88">
       <c r="A88" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B88" s="29" t="inlineStr">
@@ -5908,7 +5908,7 @@
     <row r="94">
       <c r="A94" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B94" s="29" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="95">
       <c r="A95" s="42" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B95" s="30" t="inlineStr">
@@ -6010,7 +6010,7 @@
     <row r="96">
       <c r="A96" s="48" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B96" s="29" t="inlineStr">
@@ -6061,7 +6061,7 @@
     <row r="97">
       <c r="A97" s="42" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B97" s="30" t="inlineStr">
@@ -6112,7 +6112,7 @@
     <row r="98">
       <c r="A98" s="48" t="inlineStr">
         <is>
-          <t>SPSR09101211</t>
+          <t>SRSR10105965</t>
         </is>
       </c>
       <c r="B98" s="29" t="inlineStr">
@@ -6367,7 +6367,7 @@
     <row r="103">
       <c r="A103" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B103" s="23" t="inlineStr">
@@ -6418,7 +6418,7 @@
     <row r="104">
       <c r="A104" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B104" s="23" t="inlineStr">
@@ -6724,7 +6724,7 @@
     <row r="110">
       <c r="A110" s="48" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B110" s="29" t="inlineStr">
@@ -6775,7 +6775,7 @@
     <row r="111">
       <c r="A111" s="42" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B111" s="30" t="inlineStr">
@@ -6826,7 +6826,7 @@
     <row r="112">
       <c r="A112" s="48" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B112" s="29" t="inlineStr">
@@ -6877,7 +6877,7 @@
     <row r="113">
       <c r="A113" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B113" s="23" t="inlineStr">
@@ -6979,7 +6979,7 @@
     <row r="115">
       <c r="A115" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B115" s="23" t="inlineStr">
@@ -7081,7 +7081,7 @@
     <row r="117">
       <c r="A117" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B117" s="23" t="inlineStr">
@@ -7132,7 +7132,7 @@
     <row r="118">
       <c r="A118" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B118" s="23" t="inlineStr">
@@ -7183,7 +7183,7 @@
     <row r="119">
       <c r="A119" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr">
@@ -7438,7 +7438,7 @@
     <row r="124">
       <c r="A124" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B124" s="23" t="inlineStr">
@@ -7489,7 +7489,7 @@
     <row r="125">
       <c r="A125" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B125" s="23" t="inlineStr">
@@ -7540,7 +7540,7 @@
     <row r="126">
       <c r="A126" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B126" s="23" t="inlineStr">
@@ -7693,7 +7693,7 @@
     <row r="129">
       <c r="A129" s="42" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B129" s="30" t="inlineStr">
@@ -7744,7 +7744,7 @@
     <row r="130">
       <c r="A130" s="36" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B130" s="23" t="inlineStr">
@@ -7795,7 +7795,7 @@
     <row r="131">
       <c r="A131" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B131" s="23" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="132">
       <c r="A132" s="48" t="inlineStr">
         <is>
-          <t>SRPW10081312</t>
+          <t>SRSR10101358</t>
         </is>
       </c>
       <c r="B132" s="29" t="inlineStr">
@@ -7948,7 +7948,7 @@
     <row r="134">
       <c r="A134" s="48" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B134" s="29" t="inlineStr">
@@ -8152,7 +8152,7 @@
     <row r="138">
       <c r="A138" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B138" s="29" t="inlineStr">
@@ -8203,7 +8203,7 @@
     <row r="139">
       <c r="A139" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B139" s="23" t="inlineStr">
@@ -8254,7 +8254,7 @@
     <row r="140">
       <c r="A140" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B140" s="23" t="inlineStr">
@@ -8356,7 +8356,7 @@
     <row r="142">
       <c r="A142" s="48" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B142" s="29" t="inlineStr">
@@ -8560,7 +8560,7 @@
     <row r="146">
       <c r="A146" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B146" s="23" t="inlineStr">
@@ -8713,7 +8713,7 @@
     <row r="149">
       <c r="A149" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B149" s="23" t="inlineStr">
@@ -8764,7 +8764,7 @@
     <row r="150">
       <c r="A150" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B150" s="23" t="inlineStr">
@@ -8815,7 +8815,7 @@
     <row r="151">
       <c r="A151" s="42" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B151" s="30" t="inlineStr">
@@ -8917,7 +8917,7 @@
     <row r="153">
       <c r="A153" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B153" s="23" t="inlineStr">
@@ -8968,7 +8968,7 @@
     <row r="154">
       <c r="A154" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B154" s="23" t="inlineStr">
@@ -9070,7 +9070,7 @@
     <row r="156">
       <c r="A156" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B156" s="23" t="inlineStr">
@@ -9172,7 +9172,7 @@
     <row r="158">
       <c r="A158" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B158" s="23" t="inlineStr">
@@ -9223,7 +9223,7 @@
     <row r="159">
       <c r="A159" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B159" s="23" t="inlineStr">
@@ -9427,7 +9427,7 @@
     <row r="163">
       <c r="A163" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101215</t>
+          <t>SRSR10105815</t>
         </is>
       </c>
       <c r="B163" s="30" t="inlineStr">
@@ -9478,7 +9478,7 @@
     <row r="164">
       <c r="A164" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B164" s="29" t="inlineStr">
@@ -9580,7 +9580,7 @@
     <row r="166">
       <c r="A166" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B166" s="23" t="inlineStr">
@@ -9631,7 +9631,7 @@
     <row r="167">
       <c r="A167" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B167" s="23" t="inlineStr">
@@ -9682,7 +9682,7 @@
     <row r="168">
       <c r="A168" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B168" s="29" t="inlineStr">
@@ -9784,7 +9784,7 @@
     <row r="170">
       <c r="A170" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091416</t>
+          <t>SRSR10105866</t>
         </is>
       </c>
       <c r="B170" s="23" t="inlineStr">
@@ -9886,7 +9886,7 @@
     <row r="172">
       <c r="A172" s="48" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B172" s="29" t="inlineStr">
@@ -9988,7 +9988,7 @@
     <row r="174">
       <c r="A174" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101208</t>
+          <t>SRSR10105808</t>
         </is>
       </c>
       <c r="B174" s="29" t="inlineStr">
@@ -10090,7 +10090,7 @@
     <row r="176">
       <c r="A176" s="36" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B176" s="23" t="inlineStr">
@@ -10141,7 +10141,7 @@
     <row r="177">
       <c r="A177" s="42" t="inlineStr">
         <is>
-          <t>BGPW02082212</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B177" s="30" t="inlineStr">
@@ -10192,7 +10192,7 @@
     <row r="178">
       <c r="A178" s="48" t="inlineStr">
         <is>
-          <t>BGPW02082212</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B178" s="29" t="inlineStr">
@@ -10243,7 +10243,7 @@
     <row r="179">
       <c r="A179" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B179" s="23" t="inlineStr">
@@ -10294,7 +10294,7 @@
     <row r="180">
       <c r="A180" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B180" s="23" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="182">
       <c r="A182" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B182" s="23" t="inlineStr">
@@ -10600,7 +10600,7 @@
     <row r="186">
       <c r="A186" s="48" t="inlineStr">
         <is>
-          <t>BGPW02082212</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B186" s="29" t="inlineStr">
@@ -10702,7 +10702,7 @@
     <row r="188">
       <c r="A188" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B188" s="29" t="inlineStr">
@@ -10753,7 +10753,7 @@
     <row r="189">
       <c r="A189" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B189" s="23" t="inlineStr">
@@ -10804,7 +10804,7 @@
     <row r="190">
       <c r="A190" s="48" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B190" s="29" t="inlineStr">
@@ -10957,7 +10957,7 @@
     <row r="193">
       <c r="A193" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B193" s="30" t="inlineStr">
@@ -11008,7 +11008,7 @@
     <row r="194">
       <c r="A194" s="48" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B194" s="29" t="inlineStr">
@@ -11161,7 +11161,7 @@
     <row r="197">
       <c r="A197" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B197" s="30" t="inlineStr">
@@ -11212,7 +11212,7 @@
     <row r="198">
       <c r="A198" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B198" s="29" t="inlineStr">
@@ -11263,7 +11263,7 @@
     <row r="199">
       <c r="A199" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B199" s="23" t="inlineStr">
@@ -11365,7 +11365,7 @@
     <row r="201">
       <c r="A201" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B201" s="23" t="inlineStr">
@@ -11416,7 +11416,7 @@
     <row r="202">
       <c r="A202" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B202" s="23" t="inlineStr">
@@ -11467,7 +11467,7 @@
     <row r="203">
       <c r="A203" s="36" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B203" s="23" t="inlineStr">
@@ -11518,7 +11518,7 @@
     <row r="204">
       <c r="A204" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B204" s="29" t="inlineStr">
@@ -11671,7 +11671,7 @@
     <row r="207">
       <c r="A207" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B207" s="23" t="inlineStr">
@@ -11824,7 +11824,7 @@
     <row r="210">
       <c r="A210" s="36" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B210" s="23" t="inlineStr">
@@ -11875,7 +11875,7 @@
     <row r="211">
       <c r="A211" s="36" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B211" s="23" t="inlineStr">
@@ -11926,7 +11926,7 @@
     <row r="212">
       <c r="A212" s="36" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B212" s="23" t="inlineStr">
@@ -12028,7 +12028,7 @@
     <row r="214">
       <c r="A214" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B214" s="29" t="inlineStr">
@@ -12079,7 +12079,7 @@
     <row r="215">
       <c r="A215" s="42" t="inlineStr">
         <is>
-          <t>KWSP07090815</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B215" s="30" t="inlineStr">
@@ -12130,7 +12130,7 @@
     <row r="216">
       <c r="A216" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B216" s="23" t="inlineStr">
@@ -12283,7 +12283,7 @@
     <row r="219">
       <c r="A219" s="36" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B219" s="23" t="inlineStr">
@@ -12334,7 +12334,7 @@
     <row r="220">
       <c r="A220" s="36" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B220" s="23" t="inlineStr">
@@ -12385,7 +12385,7 @@
     <row r="221">
       <c r="A221" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B221" s="30" t="inlineStr">
@@ -12436,7 +12436,7 @@
     <row r="222">
       <c r="A222" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B222" s="23" t="inlineStr">
@@ -12487,7 +12487,7 @@
     <row r="223">
       <c r="A223" s="42" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B223" s="30" t="inlineStr">
@@ -12589,7 +12589,7 @@
     <row r="225">
       <c r="A225" s="42" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B225" s="30" t="inlineStr">
@@ -12640,7 +12640,7 @@
     <row r="226">
       <c r="A226" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B226" s="23" t="inlineStr">
@@ -12691,7 +12691,7 @@
     <row r="227">
       <c r="A227" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B227" s="23" t="inlineStr">
@@ -12742,7 +12742,7 @@
     <row r="228">
       <c r="A228" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B228" s="23" t="inlineStr">
@@ -12793,7 +12793,7 @@
     <row r="229">
       <c r="A229" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B229" s="23" t="inlineStr">
@@ -12844,7 +12844,7 @@
     <row r="230">
       <c r="A230" s="48" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B230" s="29" t="inlineStr">
@@ -12895,7 +12895,7 @@
     <row r="231">
       <c r="A231" s="42" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B231" s="30" t="inlineStr">
@@ -12946,7 +12946,7 @@
     <row r="232">
       <c r="A232" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B232" s="29" t="inlineStr">
@@ -13048,7 +13048,7 @@
     <row r="234">
       <c r="A234" s="48" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B234" s="29" t="inlineStr">
@@ -13099,7 +13099,7 @@
     <row r="235">
       <c r="A235" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B235" s="23" t="inlineStr">
@@ -13150,7 +13150,7 @@
     <row r="236">
       <c r="A236" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B236" s="29" t="inlineStr">
@@ -13201,7 +13201,7 @@
     <row r="237">
       <c r="A237" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B237" s="23" t="inlineStr">
@@ -13252,7 +13252,7 @@
     <row r="238">
       <c r="A238" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B238" s="23" t="inlineStr">
@@ -13303,7 +13303,7 @@
     <row r="239">
       <c r="A239" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B239" s="23" t="inlineStr">
@@ -13354,7 +13354,7 @@
     <row r="240">
       <c r="A240" s="48" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B240" s="29" t="inlineStr">
@@ -13405,7 +13405,7 @@
     <row r="241">
       <c r="A241" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B241" s="23" t="inlineStr">
@@ -13456,7 +13456,7 @@
     <row r="242">
       <c r="A242" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B242" s="23" t="inlineStr">
@@ -13507,7 +13507,7 @@
     <row r="243">
       <c r="A243" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B243" s="23" t="inlineStr">
@@ -13558,7 +13558,7 @@
     <row r="244">
       <c r="A244" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B244" s="23" t="inlineStr">
@@ -13609,7 +13609,7 @@
     <row r="245">
       <c r="A245" s="42" t="inlineStr">
         <is>
-          <t>BRKW04070207</t>
+          <t>SRSR10106444</t>
         </is>
       </c>
       <c r="B245" s="30" t="inlineStr">
@@ -13660,7 +13660,7 @@
     <row r="246">
       <c r="A246" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B246" s="23" t="inlineStr">
@@ -13711,7 +13711,7 @@
     <row r="247">
       <c r="A247" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B247" s="23" t="inlineStr">
@@ -13762,7 +13762,7 @@
     <row r="248">
       <c r="A248" s="36" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B248" s="23" t="inlineStr">
@@ -13813,7 +13813,7 @@
     <row r="249">
       <c r="A249" s="42" t="inlineStr">
         <is>
-          <t>SRPW10081312</t>
+          <t>SRSR10101358</t>
         </is>
       </c>
       <c r="B249" s="30" t="inlineStr">
@@ -13864,7 +13864,7 @@
     <row r="250">
       <c r="A250" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B250" s="23" t="inlineStr">
@@ -13915,7 +13915,7 @@
     <row r="251">
       <c r="A251" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B251" s="23" t="inlineStr">
@@ -13966,7 +13966,7 @@
     <row r="252">
       <c r="A252" s="48" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B252" s="29" t="inlineStr">
@@ -14017,7 +14017,7 @@
     <row r="253">
       <c r="A253" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B253" s="23" t="inlineStr">
@@ -14068,7 +14068,7 @@
     <row r="254">
       <c r="A254" s="36" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B254" s="23" t="inlineStr">
@@ -14119,7 +14119,7 @@
     <row r="255">
       <c r="A255" s="36" t="inlineStr">
         <is>
-          <t>PWAN08011209</t>
+          <t>SRSR10105862</t>
         </is>
       </c>
       <c r="B255" s="23" t="inlineStr">
@@ -14170,7 +14170,7 @@
     <row r="256">
       <c r="A256" s="36" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B256" s="23" t="inlineStr">
@@ -14221,7 +14221,7 @@
     <row r="257">
       <c r="A257" s="36" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B257" s="23" t="inlineStr">
@@ -14272,7 +14272,7 @@
     <row r="258">
       <c r="A258" s="36" t="inlineStr">
         <is>
-          <t>PWAN08011209</t>
+          <t>SRSR10105862</t>
         </is>
       </c>
       <c r="B258" s="23" t="inlineStr">
@@ -14374,7 +14374,7 @@
     <row r="260">
       <c r="A260" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B260" s="23" t="inlineStr">
@@ -14425,7 +14425,7 @@
     <row r="261">
       <c r="A261" s="42" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B261" s="30" t="inlineStr">
@@ -14476,7 +14476,7 @@
     <row r="262">
       <c r="A262" s="48" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B262" s="29" t="inlineStr">
@@ -14527,7 +14527,7 @@
     <row r="263">
       <c r="A263" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B263" s="23" t="inlineStr">
@@ -14629,7 +14629,7 @@
     <row r="265">
       <c r="A265" s="42" t="inlineStr">
         <is>
-          <t>KWSP07090815</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B265" s="30" t="inlineStr">
@@ -14680,7 +14680,7 @@
     <row r="266">
       <c r="A266" s="48" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B266" s="29" t="inlineStr">
@@ -14731,7 +14731,7 @@
     <row r="267">
       <c r="A267" s="42" t="inlineStr">
         <is>
-          <t>BRKW04070207</t>
+          <t>SRBG10026421</t>
         </is>
       </c>
       <c r="B267" s="30" t="inlineStr">
@@ -14884,7 +14884,7 @@
     <row r="270">
       <c r="A270" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B270" s="23" t="inlineStr">
@@ -14935,7 +14935,7 @@
     <row r="271">
       <c r="A271" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B271" s="23" t="inlineStr">
@@ -14986,7 +14986,7 @@
     <row r="272">
       <c r="A272" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B272" s="23" t="inlineStr">
@@ -15037,7 +15037,7 @@
     <row r="273">
       <c r="A273" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B273" s="23" t="inlineStr">
@@ -15088,7 +15088,7 @@
     <row r="274">
       <c r="A274" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B274" s="23" t="inlineStr">
@@ -15241,7 +15241,7 @@
     <row r="277">
       <c r="A277" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B277" s="23" t="inlineStr">
@@ -15292,7 +15292,7 @@
     <row r="278">
       <c r="A278" s="48" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B278" s="29" t="inlineStr">
@@ -15343,7 +15343,7 @@
     <row r="279">
       <c r="A279" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B279" s="23" t="inlineStr">
@@ -15394,7 +15394,7 @@
     <row r="280">
       <c r="A280" s="36" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B280" s="23" t="inlineStr">
@@ -17332,7 +17332,7 @@
     <row r="318">
       <c r="A318" s="48" t="inlineStr">
         <is>
-          <t>SPSR09101539</t>
+          <t>SRSR10106039</t>
         </is>
       </c>
       <c r="B318" s="29" t="inlineStr">
